--- a/converted/tozalangan/chinobod/Avgust/Elektr Fiderlar.xlsx
+++ b/converted/tozalangan/chinobod/Avgust/Elektr Fiderlar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
   <si>
     <t>Fiderlar Avgust Holatiga Ko'ra</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
   </si>
   <si>
     <t>С.Мирзахакимов</t>
+  </si>
+  <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
   </si>
   <si>
     <t>chinobod/Elektr Fiderlar.xlsx [Avgust], 3-qator</t>
@@ -641,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -649,10 +655,10 @@
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="14" width="26" customWidth="1"/>
+    <col min="9" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -669,8 +675,9 @@
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
+      <c r="O1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -713,13 +720,16 @@
       <c r="N2" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1">
         <v>232000</v>
@@ -731,36 +741,39 @@
         <v>37120</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>548000</v>
@@ -772,36 +785,39 @@
         <v>87680</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>1344000</v>
@@ -813,36 +829,39 @@
         <v>215040</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1">
         <v>204000</v>
@@ -854,36 +873,39 @@
         <v>32640</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1">
         <v>196000</v>
@@ -895,36 +917,39 @@
         <v>31360</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1">
         <v>447000</v>
@@ -936,36 +961,39 @@
         <v>71520</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>49</v>
+        <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
         <v>272000</v>
@@ -977,36 +1005,39 @@
         <v>43520</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>54</v>
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1">
         <v>786000</v>
@@ -1018,36 +1049,39 @@
         <v>125760</v>
       </c>
       <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>57</v>
       </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1">
         <v>1080000</v>
@@ -1059,36 +1093,39 @@
         <v>172800</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1">
         <v>780000</v>
@@ -1100,33 +1137,36 @@
         <v>124800</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>71</v>
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
